--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECCDF97-3FC6-4FED-9C50-4B3819C5A31C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3925301-C42A-49E2-89DF-C16FE3792419}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="1065">
   <si>
     <t>1С</t>
   </si>
@@ -2786,12 +2786,6 @@
     <t>ротация завода 0,3==0,24</t>
   </si>
   <si>
-    <t>SU003870</t>
-  </si>
-  <si>
-    <t>P004953</t>
-  </si>
-  <si>
     <t>Снеки «Круггетсы сочные» Фикс.вес 0,2 ТМ «Горячая штучка»</t>
   </si>
   <si>
@@ -3231,6 +3225,15 @@
   </si>
   <si>
     <t>P005476</t>
+  </si>
+  <si>
+    <t>SU004219</t>
+  </si>
+  <si>
+    <t>P005485</t>
+  </si>
+  <si>
+    <t>Снеки «Готовые круггетсы сочные» Фикс.вес 0,2 ТМ «Горячая штучка»</t>
   </si>
 </sst>
 </file>
@@ -6742,10 +6745,10 @@
         <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D11" s="4">
         <v>4301135914</v>
@@ -6769,10 +6772,10 @@
         <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D12" s="4">
         <v>4301135914</v>
@@ -6796,10 +6799,10 @@
         <v>185</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D13" s="4">
         <v>4301135914</v>
@@ -6823,10 +6826,10 @@
         <v>913</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D14" s="4">
         <v>4301135914</v>
@@ -6841,13 +6844,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D15" s="4">
         <v>4301135914</v>
@@ -6865,10 +6868,10 @@
         <v>215</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D16" s="4">
         <v>4301135990</v>
@@ -6877,7 +6880,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G16" s="1" t="e">
         <f>VLOOKUP(E16,[1]Лист1!$D:$M,10,0)</f>
@@ -6892,10 +6895,10 @@
         <v>411</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D17" s="4">
         <v>4301135990</v>
@@ -6904,7 +6907,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G17" s="1" t="e">
         <f>VLOOKUP(E17,[1]Лист1!$D:$M,10,0)</f>
@@ -6919,10 +6922,10 @@
         <v>417</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D18" s="4">
         <v>4301135990</v>
@@ -6931,7 +6934,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G18" s="1" t="e">
         <f>VLOOKUP(E18,[1]Лист1!$D:$M,10,0)</f>
@@ -6946,10 +6949,10 @@
         <v>186</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D19" s="4">
         <v>4301135990</v>
@@ -6958,7 +6961,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G19" s="1" t="e">
         <f>VLOOKUP(E19,[1]Лист1!$D:$M,10,0)</f>
@@ -6970,13 +6973,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D20" s="4">
         <v>4301135990</v>
@@ -6985,19 +6988,19 @@
         <v>4620207491881</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D21" s="4">
         <v>4301135990</v>
@@ -7006,7 +7009,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -7015,10 +7018,10 @@
         <v>74</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D22" s="4">
         <v>4301135920</v>
@@ -7027,7 +7030,7 @@
         <v>4620207491577</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G22" s="1" t="e">
         <f>VLOOKUP(E22,[1]Лист1!$D:$M,10,0)</f>
@@ -7042,10 +7045,10 @@
         <v>97</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D23" s="4">
         <v>4301135920</v>
@@ -7054,7 +7057,7 @@
         <v>4620207491577</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G23" s="1" t="e">
         <f>VLOOKUP(E23,[1]Лист1!$D:$M,10,0)</f>
@@ -7069,10 +7072,10 @@
         <v>187</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D24" s="4">
         <v>4301135920</v>
@@ -7081,7 +7084,7 @@
         <v>4620207491577</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G24" s="1" t="e">
         <f>VLOOKUP(E24,[1]Лист1!$D:$M,10,0)</f>
@@ -7093,13 +7096,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D25" s="4">
         <v>4301135920</v>
@@ -7108,19 +7111,19 @@
         <v>4620207491577</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D26" s="4">
         <v>4301135920</v>
@@ -7129,7 +7132,7 @@
         <v>4620207491577</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G26" s="1"/>
     </row>
@@ -7342,10 +7345,10 @@
         <v>188</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D35" s="4">
         <v>4301136101</v>
@@ -7354,7 +7357,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G35" s="1"/>
     </row>
@@ -7363,10 +7366,10 @@
         <v>164</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D36" s="4">
         <v>4301136101</v>
@@ -7375,7 +7378,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G36" s="1"/>
     </row>
@@ -7384,10 +7387,10 @@
         <v>165</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D37" s="4">
         <v>4301136101</v>
@@ -7396,7 +7399,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G37" s="1"/>
     </row>
@@ -8414,10 +8417,10 @@
         <v>192</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D80" s="4">
         <v>4301135753</v>
@@ -8426,14 +8429,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G80" s="1" t="e">
         <f>VLOOKUP(E80,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -8441,10 +8444,10 @@
         <v>681</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D81" s="4">
         <v>4301135753</v>
@@ -8453,14 +8456,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G81" s="1" t="e">
         <f>VLOOKUP(E81,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -8468,10 +8471,10 @@
         <v>135</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D82" s="4">
         <v>4301135753</v>
@@ -8480,14 +8483,14 @@
         <v>4620207490914</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G82" s="1" t="e">
         <f>VLOOKUP(E82,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -8495,26 +8498,26 @@
         <v>227</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>915</v>
+        <v>1062</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>916</v>
+        <v>1063</v>
       </c>
       <c r="D83" s="4">
-        <v>4301135778</v>
+        <v>4301135932</v>
       </c>
       <c r="E83" s="3">
-        <v>4620207490853</v>
+        <v>4620207491676</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>917</v>
+        <v>1064</v>
       </c>
       <c r="G83" s="1" t="e">
         <f>VLOOKUP(E83,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -8522,26 +8525,26 @@
         <v>193</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>915</v>
+        <v>1062</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>916</v>
+        <v>1063</v>
       </c>
       <c r="D84" s="4">
-        <v>4301135778</v>
+        <v>4301135932</v>
       </c>
       <c r="E84" s="3">
-        <v>4620207490853</v>
+        <v>4620207491676</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>917</v>
+        <v>1064</v>
       </c>
       <c r="G84" s="1" t="e">
         <f>VLOOKUP(E84,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -8549,26 +8552,26 @@
         <v>685</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>915</v>
+        <v>1062</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>916</v>
+        <v>1063</v>
       </c>
       <c r="D85" s="4">
-        <v>4301135778</v>
+        <v>4301135932</v>
       </c>
       <c r="E85" s="3">
-        <v>4620207490853</v>
+        <v>4620207491676</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>917</v>
+        <v>1064</v>
       </c>
       <c r="G85" s="1" t="e">
         <f>VLOOKUP(E85,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -8576,88 +8579,88 @@
         <v>75</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>915</v>
+        <v>1062</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>916</v>
+        <v>1063</v>
       </c>
       <c r="D86" s="4">
-        <v>4301135778</v>
+        <v>4301135932</v>
       </c>
       <c r="E86" s="3">
-        <v>4620207490853</v>
+        <v>4620207491676</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>917</v>
+        <v>1064</v>
       </c>
       <c r="G86" s="1" t="e">
         <f>VLOOKUP(E86,[1]Лист1!$D:$M,10,0)</f>
         <v>#N/A</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>915</v>
+        <v>1062</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>916</v>
+        <v>1063</v>
       </c>
       <c r="D87" s="4">
-        <v>4301135778</v>
+        <v>4301135932</v>
       </c>
       <c r="E87" s="3">
-        <v>4620207490853</v>
+        <v>4620207491676</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>917</v>
+        <v>1064</v>
       </c>
       <c r="G87" s="1"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>915</v>
+        <v>1062</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>916</v>
+        <v>1063</v>
       </c>
       <c r="D88" s="4">
-        <v>4301135778</v>
+        <v>4301135932</v>
       </c>
       <c r="E88" s="3">
-        <v>4620207490853</v>
+        <v>4620207491676</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>917</v>
+        <v>1064</v>
       </c>
       <c r="G88" s="1"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>915</v>
+        <v>1062</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>916</v>
+        <v>1063</v>
       </c>
       <c r="D89" s="4">
-        <v>4301135778</v>
+        <v>4301135932</v>
       </c>
       <c r="E89" s="3">
-        <v>4620207490853</v>
+        <v>4620207491676</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>917</v>
+        <v>1064</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -8810,10 +8813,10 @@
         <v>196</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D96" s="4">
         <v>4301137046</v>
@@ -8822,7 +8825,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G96" s="1">
         <v>180</v>
@@ -8833,10 +8836,10 @@
         <v>225</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D97" s="4">
         <v>4301137046</v>
@@ -8845,7 +8848,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G97" s="1">
         <v>180</v>
@@ -8856,10 +8859,10 @@
         <v>339</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D98" s="4">
         <v>4301137046</v>
@@ -8868,7 +8871,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G98" s="1">
         <v>180</v>
@@ -8879,10 +8882,10 @@
         <v>367</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D99" s="4">
         <v>4301137046</v>
@@ -8891,7 +8894,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G99" s="1">
         <v>180</v>
@@ -8902,10 +8905,10 @@
         <v>76</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D100" s="4">
         <v>4301137046</v>
@@ -8914,7 +8917,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G100" s="1">
         <v>180</v>
@@ -8925,10 +8928,10 @@
         <v>539</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D101" s="4">
         <v>4301137046</v>
@@ -8937,7 +8940,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G101" s="1">
         <v>180</v>
@@ -8948,10 +8951,10 @@
         <v>575</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D102" s="4">
         <v>4301137046</v>
@@ -8960,7 +8963,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G102" s="1">
         <v>180</v>
@@ -8968,13 +8971,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D103" s="4">
         <v>4301137046</v>
@@ -8983,7 +8986,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G103" s="1">
         <v>180</v>
@@ -8994,10 +8997,10 @@
         <v>574</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D104" s="4">
         <v>4301137046</v>
@@ -9006,7 +9009,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G104" s="1">
         <v>180</v>
@@ -9178,7 +9181,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>742</v>
@@ -9418,7 +9421,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>721</v>
@@ -9685,10 +9688,10 @@
         <v>331</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D133" s="4">
         <v>4301135940</v>
@@ -9697,7 +9700,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G133" s="1"/>
     </row>
@@ -9706,10 +9709,10 @@
         <v>338</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D134" s="4">
         <v>4301135940</v>
@@ -9718,7 +9721,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G134" s="1"/>
     </row>
@@ -9727,10 +9730,10 @@
         <v>412</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D135" s="4">
         <v>4301135940</v>
@@ -9739,7 +9742,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G135" s="1"/>
     </row>
@@ -9748,10 +9751,10 @@
         <v>421</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D136" s="4">
         <v>4301135940</v>
@@ -9760,7 +9763,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G136" s="1"/>
     </row>
@@ -9769,10 +9772,10 @@
         <v>687</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D137" s="4">
         <v>4301135940</v>
@@ -9781,7 +9784,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G137" s="1"/>
     </row>
@@ -9790,10 +9793,10 @@
         <v>201</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D138" s="4">
         <v>4301135940</v>
@@ -9802,7 +9805,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G138" s="1"/>
     </row>
@@ -11200,10 +11203,10 @@
         <v>109</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="D197" s="4">
         <v>4301071109</v>
@@ -11212,7 +11215,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G197" s="1">
         <f>VLOOKUP(E197,[1]Лист1!$D:$M,10,0)</f>
@@ -11224,10 +11227,10 @@
         <v>88</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="D198" s="4">
         <v>4301071109</v>
@@ -11236,7 +11239,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G198" s="1">
         <f>VLOOKUP(E198,[1]Лист1!$D:$M,10,0)</f>
@@ -11248,10 +11251,10 @@
         <v>150</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D199" s="4">
         <v>4301071107</v>
@@ -11260,7 +11263,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="G199" s="1">
         <f>VLOOKUP(E199,[1]Лист1!$D:$M,10,0)</f>
@@ -11272,10 +11275,10 @@
         <v>755</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D200" s="4">
         <v>4301071107</v>
@@ -11284,7 +11287,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="G200" s="1">
         <f>VLOOKUP(E200,[1]Лист1!$D:$M,10,0)</f>
@@ -11296,10 +11299,10 @@
         <v>151</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D201" s="4">
         <v>4301071107</v>
@@ -11308,7 +11311,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="G201" s="1">
         <f>VLOOKUP(E201,[1]Лист1!$D:$M,10,0)</f>
@@ -11482,7 +11485,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>110</v>
@@ -11530,10 +11533,10 @@
         <v>111</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D211" s="4">
         <v>4301071117</v>
@@ -11542,13 +11545,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G211" s="1">
         <v>180</v>
       </c>
       <c r="H211" s="16" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -11556,10 +11559,10 @@
         <v>90</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D212" s="4">
         <v>4301071117</v>
@@ -11568,13 +11571,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G212" s="1">
         <v>180</v>
       </c>
       <c r="H212" s="16" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -11876,10 +11879,10 @@
         <v>183</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D225" s="4">
         <v>4301135946</v>
@@ -11888,7 +11891,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G225" s="1"/>
     </row>
@@ -11897,10 +11900,10 @@
         <v>112</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D226" s="4">
         <v>4301135946</v>
@@ -11909,7 +11912,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G226" s="1"/>
     </row>
@@ -11918,10 +11921,10 @@
         <v>758</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D227" s="4">
         <v>4301135946</v>
@@ -11930,7 +11933,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G227" s="1"/>
     </row>
@@ -11939,10 +11942,10 @@
         <v>92</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D228" s="4">
         <v>4301135946</v>
@@ -11951,7 +11954,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G228" s="1"/>
     </row>
@@ -13207,10 +13210,10 @@
         <v>402</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D281" s="4">
         <v>4301135984</v>
@@ -13228,10 +13231,10 @@
         <v>322</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D282" s="4">
         <v>4301135984</v>
@@ -13249,10 +13252,10 @@
         <v>871</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D283" s="4">
         <v>4301135984</v>
@@ -13267,13 +13270,13 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D284" s="4">
         <v>4301135984</v>
@@ -13288,13 +13291,13 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D285" s="4">
         <v>4301135984</v>
@@ -13312,10 +13315,10 @@
         <v>321</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D286" s="4">
         <v>4301135984</v>
@@ -14555,7 +14558,7 @@
         <v>510</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D339" s="4">
         <v>4301071141</v>
@@ -14564,7 +14567,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F339" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G339" s="1"/>
     </row>
@@ -14576,7 +14579,7 @@
         <v>510</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D340" s="4">
         <v>4301071141</v>
@@ -14585,7 +14588,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F340" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G340" s="1"/>
     </row>
@@ -14597,7 +14600,7 @@
         <v>510</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D341" s="4">
         <v>4301071141</v>
@@ -14606,7 +14609,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F341" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G341" s="1"/>
     </row>
@@ -14618,7 +14621,7 @@
         <v>510</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D342" s="4">
         <v>4301071141</v>
@@ -14627,7 +14630,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F342" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G342" s="1"/>
     </row>
@@ -14975,10 +14978,10 @@
         <v>566</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="D359" s="4">
         <v>4301135824</v>
@@ -14987,7 +14990,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F359" s="5" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G359" s="1"/>
     </row>
@@ -14996,10 +14999,10 @@
         <v>748</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="D360" s="4">
         <v>4301135824</v>
@@ -15008,7 +15011,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G360" s="1"/>
     </row>
@@ -15017,10 +15020,10 @@
         <v>540</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="D361" s="4">
         <v>4301135824</v>
@@ -15029,7 +15032,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F361" s="5" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G361" s="1"/>
     </row>
@@ -16172,10 +16175,10 @@
         <v>757</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="D416" s="4">
         <v>4301135591</v>
@@ -16184,7 +16187,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="G416" s="1">
         <v>180</v>
@@ -16195,10 +16198,10 @@
         <v>851</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="D417" s="4">
         <v>4301135591</v>
@@ -16207,7 +16210,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="G417" s="1">
         <v>180</v>
@@ -16218,10 +16221,10 @@
         <v>688</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="D418" s="4">
         <v>4301135591</v>
@@ -16230,7 +16233,7 @@
         <v>4607111036568</v>
       </c>
       <c r="F418" s="5" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="G418" s="1">
         <v>180</v>
@@ -16811,10 +16814,10 @@
         <v>867</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="D445" s="4">
         <v>4301135826</v>
@@ -16834,10 +16837,10 @@
         <v>873</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="D446" s="4">
         <v>4301135826</v>
@@ -16857,10 +16860,10 @@
         <v>874</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="D447" s="4">
         <v>4301135826</v>
@@ -16880,10 +16883,10 @@
         <v>858</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="D448" s="4">
         <v>4301135826</v>
@@ -17284,10 +17287,10 @@
         <v>632</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C466" s="3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D466" s="4">
         <v>4301135920</v>
@@ -17296,7 +17299,7 @@
         <v>4620207491577</v>
       </c>
       <c r="F466" s="5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G466" s="1"/>
       <c r="H466" s="16" t="s">
@@ -17332,10 +17335,10 @@
         <v>903</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D468" s="4">
         <v>4301135990</v>
@@ -17344,7 +17347,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F468" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G468" s="1"/>
     </row>
@@ -17434,13 +17437,13 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
+        <v>922</v>
+      </c>
+      <c r="B473" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C473" s="3" t="s">
         <v>924</v>
-      </c>
-      <c r="B473" s="3" t="s">
-        <v>925</v>
-      </c>
-      <c r="C473" s="3" t="s">
-        <v>926</v>
       </c>
       <c r="D473" s="4">
         <v>4301135753</v>
@@ -17449,13 +17452,13 @@
         <v>4620207490914</v>
       </c>
       <c r="F473" s="5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G473" s="1"/>
     </row>
     <row r="474" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>845</v>
@@ -17476,7 +17479,7 @@
     </row>
     <row r="475" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B475" s="3" t="s">
         <v>842</v>
@@ -17497,13 +17500,13 @@
     </row>
     <row r="476" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C476" s="3" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="D476" s="4">
         <v>4301071075</v>
@@ -17512,19 +17515,19 @@
         <v>4620207491102</v>
       </c>
       <c r="F476" s="5" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G476" s="1"/>
     </row>
     <row r="477" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A477" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="B477" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="C477" s="3" t="s">
         <v>932</v>
-      </c>
-      <c r="B477" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="C477" s="3" t="s">
-        <v>934</v>
       </c>
       <c r="D477" s="4">
         <v>4301071075</v>
@@ -17533,7 +17536,7 @@
         <v>4620207491102</v>
       </c>
       <c r="F477" s="5" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G477" s="1"/>
     </row>
@@ -17563,10 +17566,10 @@
         <v>727</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D479" s="4">
         <v>4301135946</v>
@@ -17575,19 +17578,19 @@
         <v>4620207491553</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G479" s="1"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D480" s="4">
         <v>4301135753</v>
@@ -17596,7 +17599,7 @@
         <v>4620207490914</v>
       </c>
       <c r="F480" s="5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G480" s="1"/>
     </row>
@@ -17689,10 +17692,10 @@
         <v>686</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C485" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D485" s="4">
         <v>4301135940</v>
@@ -17701,7 +17704,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F485" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G485" s="1"/>
     </row>
@@ -17770,13 +17773,13 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="C489" s="3" t="s">
         <v>938</v>
-      </c>
-      <c r="B489" s="3" t="s">
-        <v>939</v>
-      </c>
-      <c r="C489" s="3" t="s">
-        <v>940</v>
       </c>
       <c r="D489" s="4">
         <v>4301071094</v>
@@ -17785,19 +17788,19 @@
         <v>4620207491140</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G489" s="1"/>
     </row>
     <row r="490" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
+        <v>940</v>
+      </c>
+      <c r="B490" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="C490" s="3" t="s">
         <v>942</v>
-      </c>
-      <c r="B490" s="3" t="s">
-        <v>943</v>
-      </c>
-      <c r="C490" s="3" t="s">
-        <v>944</v>
       </c>
       <c r="D490" s="4">
         <v>4301071093</v>
@@ -17806,13 +17809,13 @@
         <v>4620207490709</v>
       </c>
       <c r="F490" s="5" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="G490" s="1"/>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>721</v>
@@ -17833,7 +17836,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>742</v>
@@ -17854,7 +17857,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>733</v>
@@ -17875,7 +17878,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>739</v>
@@ -17896,7 +17899,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>655</v>
@@ -17917,7 +17920,7 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B496" s="3" t="s">
         <v>709</v>
@@ -17938,7 +17941,7 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>764</v>
@@ -17959,7 +17962,7 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B498" s="3" t="s">
         <v>862</v>
@@ -17980,13 +17983,13 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D499" s="4">
         <v>4301135914</v>
@@ -18001,13 +18004,13 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B500" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D500" s="4">
         <v>4301135920</v>
@@ -18016,13 +18019,13 @@
         <v>4620207491577</v>
       </c>
       <c r="F500" s="5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G500" s="1"/>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>179</v>
@@ -18043,13 +18046,13 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B502" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C502" s="3" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D502" s="4">
         <v>4301136101</v>
@@ -18058,13 +18061,13 @@
         <v>4620207491652</v>
       </c>
       <c r="F502" s="5" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G502" s="1"/>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>603</v>
@@ -18085,7 +18088,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>607</v>
@@ -18106,7 +18109,7 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>611</v>
@@ -18127,7 +18130,7 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>615</v>
@@ -18148,7 +18151,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>641</v>
@@ -18169,7 +18172,7 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>638</v>
@@ -18190,13 +18193,13 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D509" s="4">
         <v>4301135946</v>
@@ -18205,19 +18208,19 @@
         <v>4620207491553</v>
       </c>
       <c r="F509" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G509" s="1"/>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D510" s="4">
         <v>4301135753</v>
@@ -18226,19 +18229,19 @@
         <v>4620207490914</v>
       </c>
       <c r="F510" s="5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G510" s="1"/>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D511" s="4">
         <v>4301135940</v>
@@ -18247,13 +18250,13 @@
         <v>4620207491614</v>
       </c>
       <c r="F511" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G511" s="1"/>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>852</v>
@@ -18274,13 +18277,13 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>233</v>
       </c>
       <c r="C513" s="3" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D513" s="4">
         <v>4301071063</v>
@@ -18289,13 +18292,13 @@
         <v>4607111039019</v>
       </c>
       <c r="F513" s="5" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="G513" s="1"/>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>490</v>
@@ -18316,13 +18319,13 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D515" s="4">
         <v>4301135834</v>
@@ -18331,19 +18334,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F515" s="5" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="G515" s="1"/>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D516" s="4">
         <v>4301135834</v>
@@ -18352,19 +18355,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F516" s="5" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="G516" s="1"/>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D517" s="4">
         <v>4301135834</v>
@@ -18373,19 +18376,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F517" s="5" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="G517" s="1"/>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
+        <v>987</v>
+      </c>
+      <c r="B518" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="C518" s="3" t="s">
         <v>989</v>
-      </c>
-      <c r="B518" s="3" t="s">
-        <v>990</v>
-      </c>
-      <c r="C518" s="3" t="s">
-        <v>991</v>
       </c>
       <c r="D518" s="4">
         <v>4301135873</v>
@@ -18394,19 +18397,19 @@
         <v>4640242182087</v>
       </c>
       <c r="F518" s="5" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="G518" s="1"/>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
+        <v>995</v>
+      </c>
+      <c r="B519" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="C519" s="3" t="s">
         <v>997</v>
-      </c>
-      <c r="B519" s="3" t="s">
-        <v>998</v>
-      </c>
-      <c r="C519" s="3" t="s">
-        <v>999</v>
       </c>
       <c r="D519" s="4">
         <v>4301135850</v>
@@ -18415,19 +18418,19 @@
         <v>4620207491492</v>
       </c>
       <c r="F519" s="5" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="G519" s="1"/>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
+        <v>999</v>
+      </c>
+      <c r="B520" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C520" s="3" t="s">
         <v>1001</v>
-      </c>
-      <c r="B520" s="3" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C520" s="3" t="s">
-        <v>1003</v>
       </c>
       <c r="D520" s="4">
         <v>4301190117</v>
@@ -18436,19 +18439,19 @@
         <v>4620207491386</v>
       </c>
       <c r="F520" s="5" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="G520" s="1"/>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B521" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C521" s="3" t="s">
         <v>1005</v>
-      </c>
-      <c r="B521" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C521" s="3" t="s">
-        <v>1007</v>
       </c>
       <c r="D521" s="4">
         <v>4301190115</v>
@@ -18457,19 +18460,19 @@
         <v>4620207491362</v>
       </c>
       <c r="F521" s="5" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="G521" s="1"/>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B522" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C522" s="3" t="s">
         <v>1009</v>
-      </c>
-      <c r="B522" s="3" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C522" s="3" t="s">
-        <v>1011</v>
       </c>
       <c r="D522" s="4">
         <v>4301135865</v>
@@ -18478,19 +18481,19 @@
         <v>4620207491485</v>
       </c>
       <c r="F522" s="5" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="G522" s="1"/>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B523" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C523" s="3" t="s">
         <v>1014</v>
-      </c>
-      <c r="B523" s="3" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C523" s="3" t="s">
-        <v>1016</v>
       </c>
       <c r="D523" s="4">
         <v>4301190116</v>
@@ -18499,19 +18502,19 @@
         <v>4620207491379</v>
       </c>
       <c r="F523" s="5" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="G523" s="1"/>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="D524" s="4">
         <v>4301071112</v>
@@ -18520,19 +18523,19 @@
         <v>4620207491256</v>
       </c>
       <c r="F524" s="5" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G524" s="1"/>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B525" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C525" s="3" t="s">
         <v>1018</v>
-      </c>
-      <c r="B525" s="3" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C525" s="3" t="s">
-        <v>1020</v>
       </c>
       <c r="D525" s="4">
         <v>4301071112</v>
@@ -18541,7 +18544,7 @@
         <v>4620207491256</v>
       </c>
       <c r="F525" s="5" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G525" s="1"/>
     </row>
@@ -18670,10 +18673,10 @@
         <v>780</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D531" s="4">
         <v>4301071117</v>
@@ -18682,7 +18685,7 @@
         <v>4620207491737</v>
       </c>
       <c r="F531" s="5" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G531" s="1">
         <v>180</v>
@@ -18768,10 +18771,10 @@
         <v>784</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C535" s="3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D535" s="4">
         <v>4301135920</v>
@@ -18780,7 +18783,7 @@
         <v>4620207491577</v>
       </c>
       <c r="F535" s="5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G535" s="21"/>
       <c r="H535" s="16" t="s">
@@ -18888,10 +18891,10 @@
         <v>789</v>
       </c>
       <c r="B540" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D540" s="4">
         <v>4301135914</v>
@@ -18936,10 +18939,10 @@
         <v>791</v>
       </c>
       <c r="B542" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D542" s="4">
         <v>4301137046</v>
@@ -18948,7 +18951,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F542" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G542" s="1">
         <v>180</v>
@@ -19058,10 +19061,10 @@
         <v>796</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C547" s="3" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="D547" s="4">
         <v>4301071109</v>
@@ -19070,7 +19073,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F547" s="5" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G547" s="21"/>
       <c r="H547" s="22" t="s">
@@ -19082,10 +19085,10 @@
         <v>797</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D548" s="4">
         <v>4301135946</v>
@@ -19094,7 +19097,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F548" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G548" s="21"/>
       <c r="H548" s="22" t="s">
@@ -19194,7 +19197,7 @@
       </c>
       <c r="G552" s="21"/>
       <c r="H552" s="22" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
@@ -19298,10 +19301,10 @@
         <v>806</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C557" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D557" s="4">
         <v>4301135753</v>
@@ -19310,7 +19313,7 @@
         <v>4620207490914</v>
       </c>
       <c r="F557" s="5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G557" s="21"/>
       <c r="H557" s="22" t="s">
@@ -19322,23 +19325,23 @@
         <v>807</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>915</v>
+        <v>1062</v>
       </c>
       <c r="C558" s="3" t="s">
-        <v>916</v>
+        <v>1063</v>
       </c>
       <c r="D558" s="4">
-        <v>4301135778</v>
+        <v>4301135932</v>
       </c>
       <c r="E558" s="3">
-        <v>4620207490853</v>
+        <v>4620207491676</v>
       </c>
       <c r="F558" s="5" t="s">
-        <v>917</v>
+        <v>1064</v>
       </c>
       <c r="G558" s="21"/>
       <c r="H558" s="16" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
@@ -19418,10 +19421,10 @@
         <v>811</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C562" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D562" s="4">
         <v>4301135984</v>
@@ -19442,10 +19445,10 @@
         <v>812</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C563" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D563" s="4">
         <v>4301135990</v>
@@ -19454,7 +19457,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F563" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G563" s="21"/>
       <c r="H563" s="16" t="s">
@@ -19562,10 +19565,10 @@
         <v>817</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D568" s="4">
         <v>4301071107</v>
@@ -19574,7 +19577,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F568" s="5" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="G568" s="21"/>
       <c r="H568" s="22" t="s">
@@ -19586,10 +19589,10 @@
         <v>818</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C569" s="3" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="D569" s="4">
         <v>4301135824</v>
@@ -19598,7 +19601,7 @@
         <v>4607111039095</v>
       </c>
       <c r="F569" s="5" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G569" s="21"/>
       <c r="H569" s="22" t="s">
@@ -19778,10 +19781,10 @@
         <v>825</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="D577" s="4">
         <v>4301136101</v>
@@ -19790,7 +19793,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F577" s="5" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G577" s="21"/>
       <c r="H577" s="22" t="s">
@@ -19898,10 +19901,10 @@
         <v>830</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C582" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D582" s="4">
         <v>4301135940</v>
@@ -19910,7 +19913,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F582" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G582" s="21"/>
       <c r="H582" s="22" t="s">
@@ -20039,13 +20042,13 @@
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C588" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D588" s="4">
         <v>4301135848</v>
@@ -20054,19 +20057,19 @@
         <v>4620207491799</v>
       </c>
       <c r="F588" s="5" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G588" s="1"/>
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B589" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C589" s="3" t="s">
         <v>1027</v>
-      </c>
-      <c r="B589" s="3" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C589" s="3" t="s">
-        <v>1029</v>
       </c>
       <c r="D589" s="4">
         <v>4301135848</v>
@@ -20075,19 +20078,19 @@
         <v>4620207491799</v>
       </c>
       <c r="F589" s="5" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G589" s="1"/>
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C590" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="D590" s="4">
         <v>4301190118</v>
@@ -20096,19 +20099,19 @@
         <v>4620207491461</v>
       </c>
       <c r="F590" s="5" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="G590" s="1"/>
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B591" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C591" s="3" t="s">
         <v>1031</v>
-      </c>
-      <c r="B591" s="3" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C591" s="3" t="s">
-        <v>1033</v>
       </c>
       <c r="D591" s="4">
         <v>4301190118</v>
@@ -20117,7 +20120,7 @@
         <v>4620207491461</v>
       </c>
       <c r="F591" s="5" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="G591" s="1"/>
     </row>

--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7734F1-6716-4704-BF0C-B29D4B339D4A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114E0174-F398-436B-B0F1-5C6E28FFA2A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$591</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$593</definedName>
     <definedName name="OLE_LINK1" localSheetId="0">Лист1!$A$526</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="1077">
   <si>
     <t>1С</t>
   </si>
@@ -3252,6 +3252,24 @@
   </si>
   <si>
     <t>Чебуреки «Сочные» Весовые ТМ «Зареченские продукты» 5 кг</t>
+  </si>
+  <si>
+    <t>Пельмени «Медвежье ушко Премиум со сливочным маслом» 0,8 классическая форма ТМ «Медвежье ушко»</t>
+  </si>
+  <si>
+    <t>Пельмени «Медвежье ушко Премиум со сливочным маслом» 0,4 классическая форма ТМ «Медвежье ушко»</t>
+  </si>
+  <si>
+    <t>SU004162</t>
+  </si>
+  <si>
+    <t>P005438</t>
+  </si>
+  <si>
+    <t>SU004163</t>
+  </si>
+  <si>
+    <t>P005439</t>
   </si>
 </sst>
 </file>
@@ -6507,7 +6525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H591"/>
+  <dimension ref="A1:H593"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88" style="11" customWidth="1"/>
@@ -20112,8 +20130,50 @@
       </c>
       <c r="G591" s="1"/>
     </row>
+    <row r="592" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A592" s="10" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B592" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C592" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D592" s="4">
+        <v>4301071134</v>
+      </c>
+      <c r="E592" s="3">
+        <v>4620207491720</v>
+      </c>
+      <c r="F592" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G592" s="1"/>
+    </row>
+    <row r="593" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A593" s="10" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B593" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C593" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D593" s="4">
+        <v>4301071135</v>
+      </c>
+      <c r="E593" s="3">
+        <v>4620207491713</v>
+      </c>
+      <c r="F593" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G593" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F591" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
+  <autoFilter ref="A1:F593" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F258">
       <sortCondition ref="A1:A188"/>
     </sortState>

--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914086E9-A91D-4A35-BD69-791FBF7E29C1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF625148-D9DB-4A2E-B8A0-D45E2BC53B06}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="1086">
   <si>
     <t>1С</t>
   </si>
@@ -2747,12 +2747,6 @@
     <t>Круггетсы с сырным соусом ТМ Горячая штучка ТС Круггетсы флоу-пак 0,2 кг  ПОКОМ</t>
   </si>
   <si>
-    <t>SU003872</t>
-  </si>
-  <si>
-    <t>P004956</t>
-  </si>
-  <si>
     <t>Снеки «Круггетсы с сырным соусом» Фикс.вес 0,2 ТМ «Горячая штучка»</t>
   </si>
   <si>
@@ -3294,6 +3288,15 @@
   </si>
   <si>
     <t>Снеки «Готовая чебупицца Пепперони» Фикс.вес 0,25 ТМ «Горячая штучка»</t>
+  </si>
+  <si>
+    <t>SU004216</t>
+  </si>
+  <si>
+    <t>P005482</t>
+  </si>
+  <si>
+    <t>Снеки «Готовые круггетсы с сырным соусом» Фикс.вес 0,2 ТМ «Горячая штучка»</t>
   </si>
 </sst>
 </file>
@@ -6709,10 +6712,10 @@
         <v>317</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D7" s="4">
         <v>4301135910</v>
@@ -6721,7 +6724,7 @@
         <v>4620207491638</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G7" s="1" t="e">
         <f>VLOOKUP(E7,[1]Лист1!$D:$M,10,0)</f>
@@ -6733,10 +6736,10 @@
         <v>330</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D8" s="4">
         <v>4301135910</v>
@@ -6745,7 +6748,7 @@
         <v>4620207491638</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G8" s="1" t="e">
         <f>VLOOKUP(E8,[1]Лист1!$D:$M,10,0)</f>
@@ -6757,10 +6760,10 @@
         <v>213</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D9" s="4">
         <v>4301135910</v>
@@ -6769,7 +6772,7 @@
         <v>4620207491638</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G9" s="1" t="e">
         <f>VLOOKUP(E9,[1]Лист1!$D:$M,10,0)</f>
@@ -6781,10 +6784,10 @@
         <v>181</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D10" s="4">
         <v>4301135910</v>
@@ -6793,7 +6796,7 @@
         <v>4620207491638</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G10" s="1" t="e">
         <f>VLOOKUP(E10,[1]Лист1!$D:$M,10,0)</f>
@@ -6805,10 +6808,10 @@
         <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D11" s="4">
         <v>4301135914</v>
@@ -6832,10 +6835,10 @@
         <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D12" s="4">
         <v>4301135914</v>
@@ -6859,10 +6862,10 @@
         <v>184</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D13" s="4">
         <v>4301135914</v>
@@ -6886,10 +6889,10 @@
         <v>892</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D14" s="4">
         <v>4301135914</v>
@@ -6907,10 +6910,10 @@
         <v>899</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D15" s="4">
         <v>4301135914</v>
@@ -6928,10 +6931,10 @@
         <v>214</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="D16" s="4">
         <v>4301135990</v>
@@ -6940,7 +6943,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G16" s="1" t="e">
         <f>VLOOKUP(E16,[1]Лист1!$D:$M,10,0)</f>
@@ -6955,10 +6958,10 @@
         <v>404</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="D17" s="4">
         <v>4301135990</v>
@@ -6967,7 +6970,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G17" s="1" t="e">
         <f>VLOOKUP(E17,[1]Лист1!$D:$M,10,0)</f>
@@ -6982,10 +6985,10 @@
         <v>410</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="D18" s="4">
         <v>4301135990</v>
@@ -6994,7 +6997,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G18" s="1" t="e">
         <f>VLOOKUP(E18,[1]Лист1!$D:$M,10,0)</f>
@@ -7009,10 +7012,10 @@
         <v>185</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="D19" s="4">
         <v>4301135990</v>
@@ -7021,7 +7024,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G19" s="1" t="e">
         <f>VLOOKUP(E19,[1]Лист1!$D:$M,10,0)</f>
@@ -7033,13 +7036,13 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="D20" s="4">
         <v>4301135990</v>
@@ -7048,7 +7051,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -7057,10 +7060,10 @@
         <v>900</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="D21" s="4">
         <v>4301135990</v>
@@ -7069,7 +7072,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G21" s="1"/>
     </row>
@@ -7078,10 +7081,10 @@
         <v>74</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D22" s="4">
         <v>4301135920</v>
@@ -7105,10 +7108,10 @@
         <v>97</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D23" s="4">
         <v>4301135920</v>
@@ -7132,10 +7135,10 @@
         <v>186</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D24" s="4">
         <v>4301135920</v>
@@ -7159,10 +7162,10 @@
         <v>895</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D25" s="4">
         <v>4301135920</v>
@@ -7180,10 +7183,10 @@
         <v>897</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D26" s="4">
         <v>4301135920</v>
@@ -7405,10 +7408,10 @@
         <v>187</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D35" s="4">
         <v>4301136101</v>
@@ -7417,7 +7420,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G35" s="1"/>
     </row>
@@ -7426,10 +7429,10 @@
         <v>164</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D36" s="4">
         <v>4301136101</v>
@@ -7438,7 +7441,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G36" s="1"/>
     </row>
@@ -7447,10 +7450,10 @@
         <v>165</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D37" s="4">
         <v>4301136101</v>
@@ -7459,7 +7462,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G37" s="1"/>
     </row>
@@ -7540,10 +7543,10 @@
         <v>555</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D41" s="4">
         <v>4301137074</v>
@@ -7552,7 +7555,7 @@
         <v>4620207492116</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G41" s="1">
         <v>180</v>
@@ -7563,10 +7566,10 @@
         <v>615</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D42" s="4">
         <v>4301137074</v>
@@ -7575,7 +7578,7 @@
         <v>4620207492116</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G42" s="1">
         <v>180</v>
@@ -7586,10 +7589,10 @@
         <v>557</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D43" s="4">
         <v>4301137074</v>
@@ -7598,7 +7601,7 @@
         <v>4620207492116</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G43" s="1">
         <v>180</v>
@@ -7609,10 +7612,10 @@
         <v>535</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D44" s="4">
         <v>4301137074</v>
@@ -7621,7 +7624,7 @@
         <v>4620207492116</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G44" s="1">
         <v>180</v>
@@ -7632,10 +7635,10 @@
         <v>130</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D45" s="4">
         <v>4301137074</v>
@@ -7644,7 +7647,7 @@
         <v>4620207492116</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G45" s="1">
         <v>180</v>
@@ -7658,10 +7661,10 @@
         <v>399</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D46" s="4">
         <v>4301137074</v>
@@ -7670,7 +7673,7 @@
         <v>4620207492116</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G46" s="1">
         <v>180</v>
@@ -7684,10 +7687,10 @@
         <v>538</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D47" s="4">
         <v>4301137074</v>
@@ -7696,7 +7699,7 @@
         <v>4620207492116</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G47" s="1">
         <v>180</v>
@@ -7710,10 +7713,10 @@
         <v>114</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D48" s="4">
         <v>4301137074</v>
@@ -7722,7 +7725,7 @@
         <v>4620207492116</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G48" s="1">
         <v>180</v>
@@ -7952,10 +7955,10 @@
         <v>384</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D58" s="4">
         <v>4301135392</v>
@@ -7964,7 +7967,7 @@
         <v>4607111039132</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G58" s="1">
         <v>180</v>
@@ -7975,10 +7978,10 @@
         <v>387</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D59" s="4">
         <v>4301135392</v>
@@ -7987,7 +7990,7 @@
         <v>4607111039132</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G59" s="1">
         <v>180</v>
@@ -7998,10 +8001,10 @@
         <v>398</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D60" s="4">
         <v>4301135392</v>
@@ -8010,7 +8013,7 @@
         <v>4607111039132</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G60" s="1">
         <v>180</v>
@@ -8021,10 +8024,10 @@
         <v>282</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D61" s="4">
         <v>4301135392</v>
@@ -8033,7 +8036,7 @@
         <v>4607111039132</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G61" s="1">
         <v>180</v>
@@ -8044,10 +8047,10 @@
         <v>533</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D62" s="4">
         <v>4301135392</v>
@@ -8056,7 +8059,7 @@
         <v>4607111039132</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G62" s="1">
         <v>180</v>
@@ -8067,10 +8070,10 @@
         <v>543</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D63" s="4">
         <v>4301135392</v>
@@ -8079,7 +8082,7 @@
         <v>4607111039132</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G63" s="1">
         <v>180</v>
@@ -8090,10 +8093,10 @@
         <v>133</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D64" s="4">
         <v>4301135392</v>
@@ -8102,7 +8105,7 @@
         <v>4607111039132</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G64" s="1">
         <v>180</v>
@@ -8477,26 +8480,23 @@
         <v>191</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>902</v>
+        <v>1083</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>903</v>
+        <v>1084</v>
       </c>
       <c r="D80" s="4">
-        <v>4301135753</v>
+        <v>4301135926</v>
       </c>
       <c r="E80" s="3">
-        <v>4620207490914</v>
+        <v>4620207491669</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>904</v>
-      </c>
-      <c r="G80" s="1" t="e">
-        <f>VLOOKUP(E80,[1]Лист1!$D:$M,10,0)</f>
-        <v>#N/A</v>
-      </c>
+        <v>1085</v>
+      </c>
+      <c r="G80" s="1"/>
       <c r="H80" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -8504,26 +8504,23 @@
         <v>662</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>902</v>
+        <v>1083</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>903</v>
+        <v>1084</v>
       </c>
       <c r="D81" s="4">
-        <v>4301135753</v>
+        <v>4301135926</v>
       </c>
       <c r="E81" s="3">
-        <v>4620207490914</v>
+        <v>4620207491669</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>904</v>
-      </c>
-      <c r="G81" s="1" t="e">
-        <f>VLOOKUP(E81,[1]Лист1!$D:$M,10,0)</f>
-        <v>#N/A</v>
-      </c>
+        <v>1085</v>
+      </c>
+      <c r="G81" s="1"/>
       <c r="H81" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -8531,26 +8528,23 @@
         <v>135</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>902</v>
+        <v>1083</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>903</v>
+        <v>1084</v>
       </c>
       <c r="D82" s="4">
-        <v>4301135753</v>
+        <v>4301135926</v>
       </c>
       <c r="E82" s="3">
-        <v>4620207490914</v>
+        <v>4620207491669</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>904</v>
-      </c>
-      <c r="G82" s="1" t="e">
-        <f>VLOOKUP(E82,[1]Лист1!$D:$M,10,0)</f>
-        <v>#N/A</v>
-      </c>
+        <v>1085</v>
+      </c>
+      <c r="G82" s="1"/>
       <c r="H82" s="16" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -8558,10 +8552,10 @@
         <v>226</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D83" s="4">
         <v>4301135932</v>
@@ -8570,7 +8564,7 @@
         <v>4620207491676</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G83" s="1" t="e">
         <f>VLOOKUP(E83,[1]Лист1!$D:$M,10,0)</f>
@@ -8585,10 +8579,10 @@
         <v>192</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D84" s="4">
         <v>4301135932</v>
@@ -8597,7 +8591,7 @@
         <v>4620207491676</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G84" s="1" t="e">
         <f>VLOOKUP(E84,[1]Лист1!$D:$M,10,0)</f>
@@ -8612,10 +8606,10 @@
         <v>666</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D85" s="4">
         <v>4301135932</v>
@@ -8624,7 +8618,7 @@
         <v>4620207491676</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G85" s="1" t="e">
         <f>VLOOKUP(E85,[1]Лист1!$D:$M,10,0)</f>
@@ -8639,10 +8633,10 @@
         <v>75</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D86" s="4">
         <v>4301135932</v>
@@ -8651,7 +8645,7 @@
         <v>4620207491676</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G86" s="1" t="e">
         <f>VLOOKUP(E86,[1]Лист1!$D:$M,10,0)</f>
@@ -8663,13 +8657,13 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D87" s="4">
         <v>4301135932</v>
@@ -8678,7 +8672,7 @@
         <v>4620207491676</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G87" s="1"/>
     </row>
@@ -8687,10 +8681,10 @@
         <v>894</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D88" s="4">
         <v>4301135932</v>
@@ -8699,7 +8693,7 @@
         <v>4620207491676</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G88" s="1"/>
     </row>
@@ -8708,10 +8702,10 @@
         <v>898</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D89" s="4">
         <v>4301135932</v>
@@ -8720,7 +8714,7 @@
         <v>4620207491676</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G89" s="1"/>
     </row>
@@ -8873,10 +8867,10 @@
         <v>195</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D96" s="4">
         <v>4301137046</v>
@@ -8885,7 +8879,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G96" s="1">
         <v>180</v>
@@ -8896,10 +8890,10 @@
         <v>224</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D97" s="4">
         <v>4301137046</v>
@@ -8908,7 +8902,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G97" s="1">
         <v>180</v>
@@ -8919,10 +8913,10 @@
         <v>332</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D98" s="4">
         <v>4301137046</v>
@@ -8931,7 +8925,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G98" s="1">
         <v>180</v>
@@ -8942,10 +8936,10 @@
         <v>360</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D99" s="4">
         <v>4301137046</v>
@@ -8954,7 +8948,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G99" s="1">
         <v>180</v>
@@ -8965,10 +8959,10 @@
         <v>76</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D100" s="4">
         <v>4301137046</v>
@@ -8977,7 +8971,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G100" s="1">
         <v>180</v>
@@ -8988,10 +8982,10 @@
         <v>531</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D101" s="4">
         <v>4301137046</v>
@@ -9000,7 +8994,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G101" s="1">
         <v>180</v>
@@ -9011,10 +9005,10 @@
         <v>563</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D102" s="4">
         <v>4301137046</v>
@@ -9023,7 +9017,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G102" s="1">
         <v>180</v>
@@ -9031,13 +9025,13 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D103" s="4">
         <v>4301137046</v>
@@ -9046,7 +9040,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G103" s="1">
         <v>180</v>
@@ -9057,10 +9051,10 @@
         <v>562</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D104" s="4">
         <v>4301137046</v>
@@ -9069,7 +9063,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G104" s="1">
         <v>180</v>
@@ -9241,7 +9235,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>721</v>
@@ -9481,7 +9475,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>700</v>
@@ -9628,10 +9622,10 @@
         <v>366</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D128" s="4">
         <v>4301132226</v>
@@ -9640,7 +9634,7 @@
         <v>4620207490631</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G128" s="1" t="e">
         <f>VLOOKUP(E128,[1]Лист1!$D:$M,10,0)</f>
@@ -9652,10 +9646,10 @@
         <v>368</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D129" s="4">
         <v>4301132226</v>
@@ -9664,7 +9658,7 @@
         <v>4620207490631</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G129" s="1" t="e">
         <f>VLOOKUP(E129,[1]Лист1!$D:$M,10,0)</f>
@@ -9676,10 +9670,10 @@
         <v>377</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D130" s="4">
         <v>4301132226</v>
@@ -9688,7 +9682,7 @@
         <v>4620207490631</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G130" s="1" t="e">
         <f>VLOOKUP(E130,[1]Лист1!$D:$M,10,0)</f>
@@ -9700,10 +9694,10 @@
         <v>286</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D131" s="4">
         <v>4301132226</v>
@@ -9712,7 +9706,7 @@
         <v>4620207490631</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G131" s="1" t="e">
         <f>VLOOKUP(E131,[1]Лист1!$D:$M,10,0)</f>
@@ -9724,10 +9718,10 @@
         <v>80</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D132" s="4">
         <v>4301132226</v>
@@ -9736,7 +9730,7 @@
         <v>4620207490631</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G132" s="1" t="e">
         <f>VLOOKUP(E132,[1]Лист1!$D:$M,10,0)</f>
@@ -9748,10 +9742,10 @@
         <v>324</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D133" s="4">
         <v>4301135940</v>
@@ -9760,7 +9754,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G133" s="1"/>
     </row>
@@ -9769,10 +9763,10 @@
         <v>331</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D134" s="4">
         <v>4301135940</v>
@@ -9781,7 +9775,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G134" s="1"/>
     </row>
@@ -9790,10 +9784,10 @@
         <v>405</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D135" s="4">
         <v>4301135940</v>
@@ -9802,7 +9796,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G135" s="1"/>
     </row>
@@ -9811,10 +9805,10 @@
         <v>414</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D136" s="4">
         <v>4301135940</v>
@@ -9823,7 +9817,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G136" s="1"/>
     </row>
@@ -9832,10 +9826,10 @@
         <v>668</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D137" s="4">
         <v>4301135940</v>
@@ -9844,7 +9838,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G137" s="1"/>
     </row>
@@ -9853,10 +9847,10 @@
         <v>200</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D138" s="4">
         <v>4301135940</v>
@@ -9865,7 +9859,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G138" s="1"/>
     </row>
@@ -11263,10 +11257,10 @@
         <v>109</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="D197" s="4">
         <v>4301071109</v>
@@ -11275,7 +11269,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G197" s="1">
         <f>VLOOKUP(E197,[1]Лист1!$D:$M,10,0)</f>
@@ -11287,10 +11281,10 @@
         <v>88</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="D198" s="4">
         <v>4301071109</v>
@@ -11299,7 +11293,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G198" s="1">
         <f>VLOOKUP(E198,[1]Лист1!$D:$M,10,0)</f>
@@ -11311,10 +11305,10 @@
         <v>150</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="D199" s="4">
         <v>4301071107</v>
@@ -11323,7 +11317,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G199" s="1">
         <f>VLOOKUP(E199,[1]Лист1!$D:$M,10,0)</f>
@@ -11335,10 +11329,10 @@
         <v>734</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="D200" s="4">
         <v>4301071107</v>
@@ -11347,7 +11341,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G200" s="1">
         <f>VLOOKUP(E200,[1]Лист1!$D:$M,10,0)</f>
@@ -11359,10 +11353,10 @@
         <v>151</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="D201" s="4">
         <v>4301071107</v>
@@ -11371,7 +11365,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G201" s="1">
         <f>VLOOKUP(E201,[1]Лист1!$D:$M,10,0)</f>
@@ -11545,7 +11539,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="10" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>110</v>
@@ -11593,10 +11587,10 @@
         <v>111</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D211" s="4">
         <v>4301071117</v>
@@ -11605,13 +11599,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G211" s="1">
         <v>180</v>
       </c>
       <c r="H211" s="16" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -11619,10 +11613,10 @@
         <v>90</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D212" s="4">
         <v>4301071117</v>
@@ -11631,13 +11625,13 @@
         <v>4620207491737</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G212" s="1">
         <v>180</v>
       </c>
       <c r="H212" s="16" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -11939,10 +11933,10 @@
         <v>182</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D225" s="4">
         <v>4301135946</v>
@@ -11951,7 +11945,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G225" s="1"/>
     </row>
@@ -11960,10 +11954,10 @@
         <v>112</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D226" s="4">
         <v>4301135946</v>
@@ -11972,7 +11966,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G226" s="1"/>
     </row>
@@ -11981,10 +11975,10 @@
         <v>737</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D227" s="4">
         <v>4301135946</v>
@@ -11993,7 +11987,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G227" s="1"/>
     </row>
@@ -12002,10 +11996,10 @@
         <v>92</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D228" s="4">
         <v>4301135946</v>
@@ -12014,7 +12008,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G228" s="1"/>
     </row>
@@ -12214,10 +12208,10 @@
         <v>738</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D237" s="4">
         <v>4301137008</v>
@@ -12226,7 +12220,7 @@
         <v>4620207491782</v>
       </c>
       <c r="F237" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G237" s="1" t="e">
         <f>VLOOKUP(E237,[1]Лист1!$D:$M,10,0)</f>
@@ -12238,10 +12232,10 @@
         <v>430</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D238" s="4">
         <v>4301137008</v>
@@ -12250,7 +12244,7 @@
         <v>4620207491782</v>
       </c>
       <c r="F238" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G238" s="1" t="e">
         <f>VLOOKUP(E238,[1]Лист1!$D:$M,10,0)</f>
@@ -12262,10 +12256,10 @@
         <v>179</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D239" s="4">
         <v>4301137008</v>
@@ -12274,7 +12268,7 @@
         <v>4620207491782</v>
       </c>
       <c r="F239" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G239" s="1" t="e">
         <f>VLOOKUP(E239,[1]Лист1!$D:$M,10,0)</f>
@@ -12286,10 +12280,10 @@
         <v>180</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D240" s="4">
         <v>4301137008</v>
@@ -12298,7 +12292,7 @@
         <v>4620207491782</v>
       </c>
       <c r="F240" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G240" s="1" t="e">
         <f>VLOOKUP(E240,[1]Лист1!$D:$M,10,0)</f>
@@ -12310,10 +12304,10 @@
         <v>93</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D241" s="4">
         <v>4301135956</v>
@@ -12322,7 +12316,7 @@
         <v>4620207491560</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G241" s="1"/>
     </row>
@@ -12331,10 +12325,10 @@
         <v>336</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D242" s="4">
         <v>4301135956</v>
@@ -12343,7 +12337,7 @@
         <v>4620207491560</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G242" s="1"/>
     </row>
@@ -12352,10 +12346,10 @@
         <v>740</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D243" s="4">
         <v>4301135956</v>
@@ -12364,7 +12358,7 @@
         <v>4620207491560</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G243" s="1"/>
     </row>
@@ -12373,10 +12367,10 @@
         <v>665</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D244" s="4">
         <v>4301135956</v>
@@ -12385,7 +12379,7 @@
         <v>4620207491560</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G244" s="1"/>
     </row>
@@ -12394,10 +12388,10 @@
         <v>211</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D245" s="4">
         <v>4301135956</v>
@@ -12406,7 +12400,7 @@
         <v>4620207491560</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G245" s="1"/>
     </row>
@@ -12415,10 +12409,10 @@
         <v>212</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D246" s="4">
         <v>4301135962</v>
@@ -12427,7 +12421,7 @@
         <v>4620207491584</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G246" s="1"/>
     </row>
@@ -12436,10 +12430,10 @@
         <v>739</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D247" s="4">
         <v>4301135962</v>
@@ -12448,7 +12442,7 @@
         <v>4620207491584</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G247" s="1"/>
     </row>
@@ -12457,10 +12451,10 @@
         <v>113</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D248" s="4">
         <v>4301135962</v>
@@ -12469,7 +12463,7 @@
         <v>4620207491584</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G248" s="1"/>
     </row>
@@ -12478,10 +12472,10 @@
         <v>94</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D249" s="4">
         <v>4301135962</v>
@@ -12490,7 +12484,7 @@
         <v>4620207491584</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G249" s="1"/>
     </row>
@@ -12502,7 +12496,7 @@
         <v>290</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D250" s="4">
         <v>4301136116</v>
@@ -12511,7 +12505,7 @@
         <v>4620207492147</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G250" s="1"/>
     </row>
@@ -12523,7 +12517,7 @@
         <v>290</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D251" s="4">
         <v>4301136116</v>
@@ -12532,7 +12526,7 @@
         <v>4620207492147</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G251" s="1"/>
     </row>
@@ -12544,7 +12538,7 @@
         <v>290</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D252" s="4">
         <v>4301136116</v>
@@ -12553,7 +12547,7 @@
         <v>4620207492147</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G252" s="1"/>
     </row>
@@ -12565,7 +12559,7 @@
         <v>290</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D253" s="4">
         <v>4301136116</v>
@@ -12574,7 +12568,7 @@
         <v>4620207492147</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G253" s="1"/>
     </row>
@@ -12586,7 +12580,7 @@
         <v>290</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D254" s="4">
         <v>4301136116</v>
@@ -12595,7 +12589,7 @@
         <v>4620207492147</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G254" s="1"/>
     </row>
@@ -12607,7 +12601,7 @@
         <v>291</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="D255" s="4">
         <v>4301136112</v>
@@ -12616,7 +12610,7 @@
         <v>4620207492154</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G255" s="1" t="e">
         <f>VLOOKUP(E255,[1]Лист1!$D:$M,10,0)</f>
@@ -12631,7 +12625,7 @@
         <v>291</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="D256" s="4">
         <v>4301136112</v>
@@ -12640,7 +12634,7 @@
         <v>4620207492154</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G256" s="1" t="e">
         <f>VLOOKUP(E256,[1]Лист1!$D:$M,10,0)</f>
@@ -12655,7 +12649,7 @@
         <v>291</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="D257" s="4">
         <v>4301136112</v>
@@ -12664,7 +12658,7 @@
         <v>4620207492154</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G257" s="1" t="e">
         <f>VLOOKUP(E257,[1]Лист1!$D:$M,10,0)</f>
@@ -12679,7 +12673,7 @@
         <v>291</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="D258" s="4">
         <v>4301136112</v>
@@ -12688,7 +12682,7 @@
         <v>4620207492154</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G258" s="1" t="e">
         <f>VLOOKUP(E258,[1]Лист1!$D:$M,10,0)</f>
@@ -13228,10 +13222,10 @@
         <v>395</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D281" s="4">
         <v>4301135984</v>
@@ -13249,10 +13243,10 @@
         <v>315</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D282" s="4">
         <v>4301135984</v>
@@ -13270,10 +13264,10 @@
         <v>850</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D283" s="4">
         <v>4301135984</v>
@@ -13288,13 +13282,13 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D284" s="4">
         <v>4301135984</v>
@@ -13309,13 +13303,13 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="10" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D285" s="4">
         <v>4301135984</v>
@@ -13333,10 +13327,10 @@
         <v>314</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D286" s="4">
         <v>4301135984</v>
@@ -14576,7 +14570,7 @@
         <v>503</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D339" s="4">
         <v>4301071141</v>
@@ -14585,7 +14579,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F339" s="5" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G339" s="1"/>
     </row>
@@ -14597,7 +14591,7 @@
         <v>503</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D340" s="4">
         <v>4301071141</v>
@@ -14606,7 +14600,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F340" s="5" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G340" s="1"/>
     </row>
@@ -14618,7 +14612,7 @@
         <v>503</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D341" s="4">
         <v>4301071141</v>
@@ -14627,7 +14621,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F341" s="5" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G341" s="1"/>
     </row>
@@ -14639,7 +14633,7 @@
         <v>503</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D342" s="4">
         <v>4301071141</v>
@@ -14648,7 +14642,7 @@
         <v>4620207491980</v>
       </c>
       <c r="F342" s="5" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="G342" s="1"/>
     </row>
@@ -14996,10 +14990,10 @@
         <v>554</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D359" s="4">
         <v>4301135954</v>
@@ -15008,7 +15002,7 @@
         <v>4620207491768</v>
       </c>
       <c r="F359" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G359" s="1"/>
     </row>
@@ -15017,10 +15011,10 @@
         <v>727</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D360" s="4">
         <v>4301135954</v>
@@ -15029,7 +15023,7 @@
         <v>4620207491768</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G360" s="1"/>
     </row>
@@ -15038,10 +15032,10 @@
         <v>532</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D361" s="4">
         <v>4301135954</v>
@@ -15050,7 +15044,7 @@
         <v>4620207491768</v>
       </c>
       <c r="F361" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G361" s="1"/>
     </row>
@@ -15125,7 +15119,7 @@
         <v>574</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D365" s="4">
         <v>4301137066</v>
@@ -15134,7 +15128,7 @@
         <v>4620207492109</v>
       </c>
       <c r="F365" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G365" s="1"/>
     </row>
@@ -15146,7 +15140,7 @@
         <v>574</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D366" s="4">
         <v>4301137066</v>
@@ -15155,7 +15149,7 @@
         <v>4620207492109</v>
       </c>
       <c r="F366" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G366" s="1"/>
     </row>
@@ -15167,7 +15161,7 @@
         <v>574</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D367" s="4">
         <v>4301137066</v>
@@ -15176,7 +15170,7 @@
         <v>4620207492109</v>
       </c>
       <c r="F367" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G367" s="1"/>
     </row>
@@ -15188,7 +15182,7 @@
         <v>574</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D368" s="4">
         <v>4301137066</v>
@@ -15197,7 +15191,7 @@
         <v>4620207492109</v>
       </c>
       <c r="F368" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G368" s="1"/>
     </row>
@@ -15566,7 +15560,7 @@
         <v>598</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D386" s="4">
         <v>4301071139</v>
@@ -15587,7 +15581,7 @@
         <v>598</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D387" s="4">
         <v>4301071139</v>
@@ -15608,7 +15602,7 @@
         <v>598</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D388" s="4">
         <v>4301071139</v>
@@ -15629,7 +15623,7 @@
         <v>598</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D389" s="4">
         <v>4301071139</v>
@@ -15650,7 +15644,7 @@
         <v>598</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D390" s="4">
         <v>4301071139</v>
@@ -15671,7 +15665,7 @@
         <v>601</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D391" s="4">
         <v>4301071138</v>
@@ -15692,7 +15686,7 @@
         <v>601</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D392" s="4">
         <v>4301071138</v>
@@ -15713,7 +15707,7 @@
         <v>601</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D393" s="4">
         <v>4301071138</v>
@@ -15734,7 +15728,7 @@
         <v>601</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D394" s="4">
         <v>4301071138</v>
@@ -15755,7 +15749,7 @@
         <v>601</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D395" s="4">
         <v>4301071138</v>
@@ -16193,10 +16187,10 @@
         <v>736</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="D416" s="4">
         <v>4301135912</v>
@@ -16205,7 +16199,7 @@
         <v>4620207491751</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G416" s="1">
         <v>180</v>
@@ -16216,10 +16210,10 @@
         <v>830</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="D417" s="4">
         <v>4301135912</v>
@@ -16228,7 +16222,7 @@
         <v>4620207491751</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G417" s="1">
         <v>180</v>
@@ -16239,10 +16233,10 @@
         <v>669</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="D418" s="4">
         <v>4301135912</v>
@@ -16251,7 +16245,7 @@
         <v>4620207491751</v>
       </c>
       <c r="F418" s="5" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G418" s="1">
         <v>180</v>
@@ -16832,10 +16826,10 @@
         <v>846</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D445" s="4">
         <v>4301135826</v>
@@ -16855,10 +16849,10 @@
         <v>852</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D446" s="4">
         <v>4301135826</v>
@@ -16878,10 +16872,10 @@
         <v>853</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D447" s="4">
         <v>4301135826</v>
@@ -16901,10 +16895,10 @@
         <v>837</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D448" s="4">
         <v>4301135826</v>
@@ -17260,7 +17254,7 @@
         <v>598</v>
       </c>
       <c r="C464" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D464" s="4">
         <v>4301071139</v>
@@ -17284,7 +17278,7 @@
         <v>601</v>
       </c>
       <c r="C465" s="3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D465" s="4">
         <v>4301071138</v>
@@ -17305,10 +17299,10 @@
         <v>617</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C466" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D466" s="4">
         <v>4301135920</v>
@@ -17353,10 +17347,10 @@
         <v>882</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="D468" s="4">
         <v>4301135990</v>
@@ -17365,7 +17359,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F468" s="5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G468" s="1"/>
     </row>
@@ -17458,25 +17452,25 @@
         <v>901</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>902</v>
+        <v>1083</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>903</v>
+        <v>1084</v>
       </c>
       <c r="D473" s="4">
-        <v>4301135753</v>
+        <v>4301135926</v>
       </c>
       <c r="E473" s="3">
-        <v>4620207490914</v>
+        <v>4620207491669</v>
       </c>
       <c r="F473" s="5" t="s">
-        <v>904</v>
+        <v>1085</v>
       </c>
       <c r="G473" s="1"/>
     </row>
     <row r="474" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>824</v>
@@ -17497,7 +17491,7 @@
     </row>
     <row r="475" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B475" s="3" t="s">
         <v>821</v>
@@ -17518,13 +17512,13 @@
     </row>
     <row r="476" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C476" s="3" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="D476" s="4">
         <v>4301071075</v>
@@ -17533,19 +17527,19 @@
         <v>4620207491102</v>
       </c>
       <c r="F476" s="5" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G476" s="1"/>
     </row>
     <row r="477" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A477" s="10" t="s">
+        <v>907</v>
+      </c>
+      <c r="B477" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="C477" s="3" t="s">
         <v>909</v>
-      </c>
-      <c r="B477" s="3" t="s">
-        <v>910</v>
-      </c>
-      <c r="C477" s="3" t="s">
-        <v>911</v>
       </c>
       <c r="D477" s="4">
         <v>4301071075</v>
@@ -17554,7 +17548,7 @@
         <v>4620207491102</v>
       </c>
       <c r="F477" s="5" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G477" s="1"/>
     </row>
@@ -17563,10 +17557,10 @@
         <v>690</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C478" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D478" s="4">
         <v>4301135910</v>
@@ -17575,7 +17569,7 @@
         <v>4620207491638</v>
       </c>
       <c r="F478" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G478" s="1"/>
     </row>
@@ -17584,10 +17578,10 @@
         <v>706</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D479" s="4">
         <v>4301135946</v>
@@ -17596,28 +17590,28 @@
         <v>4620207491553</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G479" s="1"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="10" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>902</v>
+        <v>1083</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>903</v>
+        <v>1084</v>
       </c>
       <c r="D480" s="4">
-        <v>4301135753</v>
+        <v>4301135926</v>
       </c>
       <c r="E480" s="3">
-        <v>4620207490914</v>
+        <v>4620207491669</v>
       </c>
       <c r="F480" s="5" t="s">
-        <v>904</v>
+        <v>1085</v>
       </c>
       <c r="G480" s="1"/>
     </row>
@@ -17710,10 +17704,10 @@
         <v>667</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C485" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D485" s="4">
         <v>4301135940</v>
@@ -17722,7 +17716,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F485" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G485" s="1"/>
     </row>
@@ -17734,7 +17728,7 @@
         <v>598</v>
       </c>
       <c r="C486" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D486" s="4">
         <v>4301071139</v>
@@ -17752,10 +17746,10 @@
         <v>624</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C487" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D487" s="4">
         <v>4301135956</v>
@@ -17764,7 +17758,7 @@
         <v>4620207491560</v>
       </c>
       <c r="F487" s="5" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G487" s="1"/>
     </row>
@@ -17773,10 +17767,10 @@
         <v>623</v>
       </c>
       <c r="B488" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C488" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D488" s="4">
         <v>4301135962</v>
@@ -17785,19 +17779,19 @@
         <v>4620207491584</v>
       </c>
       <c r="F488" s="5" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G488" s="1"/>
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A489" s="10" t="s">
+        <v>913</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="C489" s="3" t="s">
         <v>915</v>
-      </c>
-      <c r="B489" s="3" t="s">
-        <v>916</v>
-      </c>
-      <c r="C489" s="3" t="s">
-        <v>917</v>
       </c>
       <c r="D489" s="4">
         <v>4301071094</v>
@@ -17806,19 +17800,19 @@
         <v>4620207491140</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G489" s="1"/>
     </row>
     <row r="490" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A490" s="10" t="s">
+        <v>917</v>
+      </c>
+      <c r="B490" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="C490" s="3" t="s">
         <v>919</v>
-      </c>
-      <c r="B490" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="C490" s="3" t="s">
-        <v>921</v>
       </c>
       <c r="D490" s="4">
         <v>4301071093</v>
@@ -17827,13 +17821,13 @@
         <v>4620207490709</v>
       </c>
       <c r="F490" s="5" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G490" s="1"/>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="10" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>700</v>
@@ -17854,7 +17848,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="10" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>721</v>
@@ -17875,7 +17869,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="10" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>712</v>
@@ -17896,7 +17890,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="10" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>718</v>
@@ -17917,7 +17911,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="10" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>636</v>
@@ -17938,13 +17932,13 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="10" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B496" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C496" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D496" s="4">
         <v>4301135910</v>
@@ -17953,13 +17947,13 @@
         <v>4620207491638</v>
       </c>
       <c r="F496" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G496" s="1"/>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="10" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>743</v>
@@ -17980,7 +17974,7 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="10" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B498" s="3" t="s">
         <v>841</v>
@@ -18001,13 +17995,13 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="10" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D499" s="4">
         <v>4301135914</v>
@@ -18022,13 +18016,13 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="10" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B500" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D500" s="4">
         <v>4301135920</v>
@@ -18043,13 +18037,13 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="10" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C501" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D501" s="4">
         <v>4301137008</v>
@@ -18058,19 +18052,19 @@
         <v>4620207491782</v>
       </c>
       <c r="F501" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G501" s="1"/>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="10" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B502" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C502" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D502" s="4">
         <v>4301136101</v>
@@ -18079,13 +18073,13 @@
         <v>4620207491652</v>
       </c>
       <c r="F502" s="5" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G502" s="1"/>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="10" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>590</v>
@@ -18106,7 +18100,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="10" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>594</v>
@@ -18127,13 +18121,13 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="10" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>598</v>
       </c>
       <c r="C505" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D505" s="4">
         <v>4301071139</v>
@@ -18148,13 +18142,13 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="10" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>601</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D506" s="4">
         <v>4301071138</v>
@@ -18169,13 +18163,13 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="10" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D507" s="4">
         <v>4301135956</v>
@@ -18184,19 +18178,19 @@
         <v>4620207491560</v>
       </c>
       <c r="F507" s="5" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G507" s="1"/>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="10" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B508" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C508" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D508" s="4">
         <v>4301135962</v>
@@ -18205,19 +18199,19 @@
         <v>4620207491584</v>
       </c>
       <c r="F508" s="5" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G508" s="1"/>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A509" s="10" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C509" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D509" s="4">
         <v>4301135946</v>
@@ -18226,40 +18220,40 @@
         <v>4620207491553</v>
       </c>
       <c r="F509" s="5" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G509" s="1"/>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A510" s="10" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B510" s="3" t="s">
-        <v>902</v>
+        <v>1083</v>
       </c>
       <c r="C510" s="3" t="s">
-        <v>903</v>
+        <v>1084</v>
       </c>
       <c r="D510" s="4">
-        <v>4301135753</v>
+        <v>4301135926</v>
       </c>
       <c r="E510" s="3">
-        <v>4620207490914</v>
+        <v>4620207491669</v>
       </c>
       <c r="F510" s="5" t="s">
-        <v>904</v>
+        <v>1085</v>
       </c>
       <c r="G510" s="1"/>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="10" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C511" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D511" s="4">
         <v>4301135940</v>
@@ -18268,13 +18262,13 @@
         <v>4620207491614</v>
       </c>
       <c r="F511" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G511" s="1"/>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="10" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>831</v>
@@ -18295,13 +18289,13 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="10" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>232</v>
       </c>
       <c r="C513" s="3" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="D513" s="4">
         <v>4301071063</v>
@@ -18310,13 +18304,13 @@
         <v>4607111039019</v>
       </c>
       <c r="F513" s="5" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="G513" s="1"/>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="10" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>483</v>
@@ -18337,13 +18331,13 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="10" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C515" s="3" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="D515" s="4">
         <v>4301135834</v>
@@ -18352,19 +18346,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F515" s="5" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="G515" s="1"/>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="10" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C516" s="3" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="D516" s="4">
         <v>4301135834</v>
@@ -18373,19 +18367,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F516" s="5" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="G516" s="1"/>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="10" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C517" s="3" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="D517" s="4">
         <v>4301135834</v>
@@ -18394,19 +18388,19 @@
         <v>4620207491188</v>
       </c>
       <c r="F517" s="5" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="G517" s="1"/>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="10" t="s">
+        <v>961</v>
+      </c>
+      <c r="B518" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="C518" s="3" t="s">
         <v>963</v>
-      </c>
-      <c r="B518" s="3" t="s">
-        <v>964</v>
-      </c>
-      <c r="C518" s="3" t="s">
-        <v>965</v>
       </c>
       <c r="D518" s="4">
         <v>4301135873</v>
@@ -18415,19 +18409,19 @@
         <v>4640242182087</v>
       </c>
       <c r="F518" s="5" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G518" s="1"/>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="10" t="s">
+        <v>969</v>
+      </c>
+      <c r="B519" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="C519" s="3" t="s">
         <v>971</v>
-      </c>
-      <c r="B519" s="3" t="s">
-        <v>972</v>
-      </c>
-      <c r="C519" s="3" t="s">
-        <v>973</v>
       </c>
       <c r="D519" s="4">
         <v>4301135850</v>
@@ -18436,19 +18430,19 @@
         <v>4620207491492</v>
       </c>
       <c r="F519" s="5" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="G519" s="1"/>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="10" t="s">
+        <v>973</v>
+      </c>
+      <c r="B520" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="C520" s="3" t="s">
         <v>975</v>
-      </c>
-      <c r="B520" s="3" t="s">
-        <v>976</v>
-      </c>
-      <c r="C520" s="3" t="s">
-        <v>977</v>
       </c>
       <c r="D520" s="4">
         <v>4301190117</v>
@@ -18457,19 +18451,19 @@
         <v>4620207491386</v>
       </c>
       <c r="F520" s="5" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="G520" s="1"/>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="10" t="s">
+        <v>977</v>
+      </c>
+      <c r="B521" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="C521" s="3" t="s">
         <v>979</v>
-      </c>
-      <c r="B521" s="3" t="s">
-        <v>980</v>
-      </c>
-      <c r="C521" s="3" t="s">
-        <v>981</v>
       </c>
       <c r="D521" s="4">
         <v>4301190115</v>
@@ -18478,19 +18472,19 @@
         <v>4620207491362</v>
       </c>
       <c r="F521" s="5" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="G521" s="1"/>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="10" t="s">
+        <v>981</v>
+      </c>
+      <c r="B522" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="C522" s="3" t="s">
         <v>983</v>
-      </c>
-      <c r="B522" s="3" t="s">
-        <v>984</v>
-      </c>
-      <c r="C522" s="3" t="s">
-        <v>985</v>
       </c>
       <c r="D522" s="4">
         <v>4301135865</v>
@@ -18499,19 +18493,19 @@
         <v>4620207491485</v>
       </c>
       <c r="F522" s="5" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="G522" s="1"/>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="10" t="s">
+        <v>986</v>
+      </c>
+      <c r="B523" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="C523" s="3" t="s">
         <v>988</v>
-      </c>
-      <c r="B523" s="3" t="s">
-        <v>989</v>
-      </c>
-      <c r="C523" s="3" t="s">
-        <v>990</v>
       </c>
       <c r="D523" s="4">
         <v>4301190116</v>
@@ -18520,19 +18514,19 @@
         <v>4620207491379</v>
       </c>
       <c r="F523" s="5" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="G523" s="1"/>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="10" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C524" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="D524" s="4">
         <v>4301071112</v>
@@ -18541,19 +18535,19 @@
         <v>4620207491256</v>
       </c>
       <c r="F524" s="5" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="G524" s="1"/>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="10" t="s">
+        <v>990</v>
+      </c>
+      <c r="B525" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="C525" s="3" t="s">
         <v>992</v>
-      </c>
-      <c r="B525" s="3" t="s">
-        <v>993</v>
-      </c>
-      <c r="C525" s="3" t="s">
-        <v>994</v>
       </c>
       <c r="D525" s="4">
         <v>4301071112</v>
@@ -18562,7 +18556,7 @@
         <v>4620207491256</v>
       </c>
       <c r="F525" s="5" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="G525" s="1"/>
     </row>
@@ -18622,7 +18616,7 @@
         <v>601</v>
       </c>
       <c r="C528" s="3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D528" s="4">
         <v>4301071138</v>
@@ -18667,10 +18661,10 @@
         <v>758</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C530" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D530" s="4">
         <v>4301132226</v>
@@ -18679,7 +18673,7 @@
         <v>4620207490631</v>
       </c>
       <c r="F530" s="5" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G530" s="21"/>
       <c r="H530" s="22" t="s">
@@ -18691,10 +18685,10 @@
         <v>759</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C531" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D531" s="4">
         <v>4301071117</v>
@@ -18703,7 +18697,7 @@
         <v>4620207491737</v>
       </c>
       <c r="F531" s="5" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G531" s="1">
         <v>180</v>
@@ -18720,7 +18714,7 @@
         <v>291</v>
       </c>
       <c r="C532" s="3" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="D532" s="4">
         <v>4301136112</v>
@@ -18729,7 +18723,7 @@
         <v>4620207492154</v>
       </c>
       <c r="F532" s="5" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G532" s="21"/>
       <c r="H532" s="22" t="s">
@@ -18765,10 +18759,10 @@
         <v>762</v>
       </c>
       <c r="B534" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C534" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="D534" s="4">
         <v>4301135392</v>
@@ -18777,7 +18771,7 @@
         <v>4607111039132</v>
       </c>
       <c r="F534" s="5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G534" s="21"/>
       <c r="H534" s="22" t="s">
@@ -18789,10 +18783,10 @@
         <v>763</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C535" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D535" s="4">
         <v>4301135920</v>
@@ -18840,7 +18834,7 @@
         <v>598</v>
       </c>
       <c r="C537" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D537" s="4">
         <v>4301071139</v>
@@ -18861,10 +18855,10 @@
         <v>766</v>
       </c>
       <c r="B538" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C538" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D538" s="4">
         <v>4301135962</v>
@@ -18873,7 +18867,7 @@
         <v>4620207491584</v>
       </c>
       <c r="F538" s="5" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G538" s="21"/>
       <c r="H538" s="22" t="s">
@@ -18885,10 +18879,10 @@
         <v>767</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C539" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D539" s="4">
         <v>4301135956</v>
@@ -18897,7 +18891,7 @@
         <v>4620207491560</v>
       </c>
       <c r="F539" s="5" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G539" s="21"/>
       <c r="H539" s="22" t="s">
@@ -18909,10 +18903,10 @@
         <v>768</v>
       </c>
       <c r="B540" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C540" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D540" s="4">
         <v>4301135914</v>
@@ -18957,10 +18951,10 @@
         <v>770</v>
       </c>
       <c r="B542" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C542" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D542" s="4">
         <v>4301137046</v>
@@ -18969,7 +18963,7 @@
         <v>4620207492093</v>
       </c>
       <c r="F542" s="5" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G542" s="1">
         <v>180</v>
@@ -18986,7 +18980,7 @@
         <v>574</v>
       </c>
       <c r="C543" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D543" s="4">
         <v>4301137066</v>
@@ -18995,7 +18989,7 @@
         <v>4620207492109</v>
       </c>
       <c r="F543" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G543" s="21"/>
       <c r="H543" s="22" t="s">
@@ -19058,7 +19052,7 @@
         <v>290</v>
       </c>
       <c r="C546" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D546" s="4">
         <v>4301136116</v>
@@ -19067,7 +19061,7 @@
         <v>4620207492147</v>
       </c>
       <c r="F546" s="5" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G546" s="21"/>
       <c r="H546" s="22" t="s">
@@ -19079,10 +19073,10 @@
         <v>775</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C547" s="3" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="D547" s="4">
         <v>4301071109</v>
@@ -19091,7 +19085,7 @@
         <v>4607111035929</v>
       </c>
       <c r="F547" s="5" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G547" s="21"/>
       <c r="H547" s="22" t="s">
@@ -19103,10 +19097,10 @@
         <v>776</v>
       </c>
       <c r="B548" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C548" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D548" s="4">
         <v>4301135946</v>
@@ -19115,7 +19109,7 @@
         <v>4620207491553</v>
       </c>
       <c r="F548" s="5" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G548" s="21"/>
       <c r="H548" s="22" t="s">
@@ -19215,7 +19209,7 @@
       </c>
       <c r="G552" s="21"/>
       <c r="H552" s="22" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
@@ -19223,10 +19217,10 @@
         <v>781</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C553" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D553" s="4">
         <v>4301137074</v>
@@ -19235,7 +19229,7 @@
         <v>4620207492116</v>
       </c>
       <c r="F553" s="5" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G553" s="21"/>
       <c r="H553" s="22" t="s">
@@ -19319,19 +19313,19 @@
         <v>785</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>902</v>
+        <v>1083</v>
       </c>
       <c r="C557" s="3" t="s">
-        <v>903</v>
+        <v>1084</v>
       </c>
       <c r="D557" s="4">
-        <v>4301135753</v>
+        <v>4301135926</v>
       </c>
       <c r="E557" s="3">
-        <v>4620207490914</v>
+        <v>4620207491669</v>
       </c>
       <c r="F557" s="5" t="s">
-        <v>904</v>
+        <v>1085</v>
       </c>
       <c r="G557" s="21"/>
       <c r="H557" s="22" t="s">
@@ -19343,10 +19337,10 @@
         <v>786</v>
       </c>
       <c r="B558" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C558" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D558" s="4">
         <v>4301135932</v>
@@ -19355,7 +19349,7 @@
         <v>4620207491676</v>
       </c>
       <c r="F558" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G558" s="21"/>
       <c r="H558" s="16" t="s">
@@ -19439,10 +19433,10 @@
         <v>790</v>
       </c>
       <c r="B562" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C562" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D562" s="4">
         <v>4301135984</v>
@@ -19463,10 +19457,10 @@
         <v>791</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C563" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="D563" s="4">
         <v>4301135990</v>
@@ -19475,7 +19469,7 @@
         <v>4620207491881</v>
       </c>
       <c r="F563" s="5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G563" s="21"/>
       <c r="H563" s="16" t="s">
@@ -19583,10 +19577,10 @@
         <v>796</v>
       </c>
       <c r="B568" s="3" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C568" s="3" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="D568" s="4">
         <v>4301071107</v>
@@ -19595,7 +19589,7 @@
         <v>4607111035905</v>
       </c>
       <c r="F568" s="5" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="G568" s="21"/>
       <c r="H568" s="22" t="s">
@@ -19607,10 +19601,10 @@
         <v>797</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C569" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D569" s="4">
         <v>4301135954</v>
@@ -19619,7 +19613,7 @@
         <v>4620207491768</v>
       </c>
       <c r="F569" s="5" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G569" s="21"/>
       <c r="H569" s="22" t="s">
@@ -19631,10 +19625,10 @@
         <v>798</v>
       </c>
       <c r="B570" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C570" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D570" s="4">
         <v>4301137008</v>
@@ -19643,7 +19637,7 @@
         <v>4620207491782</v>
       </c>
       <c r="F570" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G570" s="21"/>
       <c r="H570" s="22" t="s">
@@ -19703,10 +19697,10 @@
         <v>800</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C573" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D573" s="4">
         <v>4301135910</v>
@@ -19715,7 +19709,7 @@
         <v>4620207491638</v>
       </c>
       <c r="F573" s="5" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G573" s="21"/>
       <c r="H573" s="22" t="s">
@@ -19799,10 +19793,10 @@
         <v>804</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D577" s="4">
         <v>4301136101</v>
@@ -19811,7 +19805,7 @@
         <v>4620207491652</v>
       </c>
       <c r="F577" s="5" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G577" s="21"/>
       <c r="H577" s="22" t="s">
@@ -19919,10 +19913,10 @@
         <v>809</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C582" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D582" s="4">
         <v>4301135940</v>
@@ -19931,7 +19925,7 @@
         <v>4620207491614</v>
       </c>
       <c r="F582" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G582" s="21"/>
       <c r="H582" s="22" t="s">
@@ -20060,13 +20054,13 @@
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" s="10" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C588" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D588" s="4">
         <v>4301135848</v>
@@ -20075,19 +20069,19 @@
         <v>4620207491799</v>
       </c>
       <c r="F588" s="5" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="G588" s="1"/>
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" s="10" t="s">
+        <v>999</v>
+      </c>
+      <c r="B589" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C589" s="3" t="s">
         <v>1001</v>
-      </c>
-      <c r="B589" s="3" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C589" s="3" t="s">
-        <v>1003</v>
       </c>
       <c r="D589" s="4">
         <v>4301135848</v>
@@ -20096,19 +20090,19 @@
         <v>4620207491799</v>
       </c>
       <c r="F589" s="5" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="G589" s="1"/>
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" s="10" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C590" s="3" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D590" s="4">
         <v>4301190118</v>
@@ -20117,19 +20111,19 @@
         <v>4620207491461</v>
       </c>
       <c r="F590" s="5" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="G590" s="1"/>
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B591" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C591" s="3" t="s">
         <v>1005</v>
-      </c>
-      <c r="B591" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C591" s="3" t="s">
-        <v>1007</v>
       </c>
       <c r="D591" s="4">
         <v>4301190118</v>
@@ -20138,19 +20132,19 @@
         <v>4620207491461</v>
       </c>
       <c r="F591" s="5" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="G591" s="1"/>
     </row>
     <row r="592" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A592" s="10" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B592" s="3" t="s">
         <v>1066</v>
       </c>
-      <c r="B592" s="3" t="s">
-        <v>1068</v>
-      </c>
       <c r="C592" s="3" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="D592" s="4">
         <v>4301071134</v>
@@ -20159,19 +20153,19 @@
         <v>4620207491720</v>
       </c>
       <c r="F592" s="5" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="G592" s="1"/>
     </row>
     <row r="593" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A593" s="10" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C593" s="3" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="D593" s="4">
         <v>4301071135</v>
@@ -20180,19 +20174,19 @@
         <v>4620207491713</v>
       </c>
       <c r="F593" s="5" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G593" s="1"/>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A594" s="10" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B594" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C594" s="3" t="s">
         <v>1072</v>
-      </c>
-      <c r="B594" s="3" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C594" s="3" t="s">
-        <v>1074</v>
       </c>
       <c r="D594" s="4">
         <v>4301132243</v>
@@ -20201,19 +20195,19 @@
         <v>4620207491195</v>
       </c>
       <c r="F594" s="5" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="G594" s="1"/>
     </row>
     <row r="595" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A595" s="10" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B595" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C595" s="3" t="s">
         <v>1075</v>
-      </c>
-      <c r="B595" s="3" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C595" s="3" t="s">
-        <v>1077</v>
       </c>
       <c r="D595" s="4">
         <v>4301080162</v>
@@ -20222,7 +20216,7 @@
         <v>4620207492178</v>
       </c>
       <c r="F595" s="5" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="G595" s="1"/>
     </row>

--- a/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
+++ b/в бланки заводов/ПОКОМ ЗПФ/pokom_zpf/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\ПОКОМ ЗПФ\pokom_zpf\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF625148-D9DB-4A2E-B8A0-D45E2BC53B06}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5317F2D-6B1C-435C-8660-CD7951492BC0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$595</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$F$597</definedName>
     <definedName name="OLE_LINK1" localSheetId="0">Лист1!$A$526</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="1086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2567" uniqueCount="1088">
   <si>
     <t>1С</t>
   </si>
@@ -3297,6 +3297,12 @@
   </si>
   <si>
     <t>Снеки «Готовые круггетсы с сырным соусом» Фикс.вес 0,2 ТМ «Горячая штучка»</t>
+  </si>
+  <si>
+    <t>Вареники Медвежье ушко Премиум с картофелем и лесными грибами клас. форма флоу-пак 0,6 кг  ПОКОМ</t>
+  </si>
+  <si>
+    <t>Пельмени Медвежье ушко Премиум со сливочным маслом 0,8 кг ТМ Медвежье ушко  ПОКОМ</t>
   </si>
 </sst>
 </file>
@@ -6552,7 +6558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H595"/>
+  <dimension ref="A1:H597"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88" style="11" customWidth="1"/>
@@ -20159,69 +20165,110 @@
     </row>
     <row r="593" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A593" s="10" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B593" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C593" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D593" s="4">
+        <v>4301071134</v>
+      </c>
+      <c r="E593" s="3">
+        <v>4620207491720</v>
+      </c>
+      <c r="F593" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G593" s="1"/>
+    </row>
+    <row r="594" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A594" s="10" t="s">
         <v>1065</v>
       </c>
-      <c r="B593" s="3" t="s">
+      <c r="B594" s="3" t="s">
         <v>1068</v>
       </c>
-      <c r="C593" s="3" t="s">
+      <c r="C594" s="3" t="s">
         <v>1069</v>
       </c>
-      <c r="D593" s="4">
+      <c r="D594" s="4">
         <v>4301071135</v>
       </c>
-      <c r="E593" s="3">
+      <c r="E594" s="3">
         <v>4620207491713</v>
       </c>
-      <c r="F593" s="5" t="s">
+      <c r="F594" s="5" t="s">
         <v>1065</v>
       </c>
-      <c r="G593" s="1"/>
-    </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A594" s="10" t="s">
+      <c r="G594" s="1"/>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A595" s="10" t="s">
         <v>1070</v>
       </c>
-      <c r="B594" s="3" t="s">
+      <c r="B595" s="3" t="s">
         <v>1071</v>
       </c>
-      <c r="C594" s="3" t="s">
+      <c r="C595" s="3" t="s">
         <v>1072</v>
       </c>
-      <c r="D594" s="4">
+      <c r="D595" s="4">
         <v>4301132243</v>
       </c>
-      <c r="E594" s="3">
+      <c r="E595" s="3">
         <v>4620207491195</v>
       </c>
-      <c r="F594" s="5" t="s">
+      <c r="F595" s="5" t="s">
         <v>1070</v>
       </c>
-      <c r="G594" s="1"/>
-    </row>
-    <row r="595" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A595" s="10" t="s">
+      <c r="G595" s="1"/>
+    </row>
+    <row r="596" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A596" s="10" t="s">
         <v>1073</v>
       </c>
-      <c r="B595" s="3" t="s">
+      <c r="B596" s="3" t="s">
         <v>1074</v>
       </c>
-      <c r="C595" s="3" t="s">
+      <c r="C596" s="3" t="s">
         <v>1075</v>
       </c>
-      <c r="D595" s="4">
+      <c r="D596" s="4">
         <v>4301080162</v>
       </c>
-      <c r="E595" s="3">
+      <c r="E596" s="3">
         <v>4620207492178</v>
       </c>
-      <c r="F595" s="5" t="s">
+      <c r="F596" s="5" t="s">
         <v>1073</v>
       </c>
-      <c r="G595" s="1"/>
+      <c r="G596" s="1"/>
+    </row>
+    <row r="597" spans="1:7" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A597" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B597" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C597" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D597" s="4">
+        <v>4301080162</v>
+      </c>
+      <c r="E597" s="3">
+        <v>4620207492178</v>
+      </c>
+      <c r="F597" s="5" t="s">
+        <v>1073</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F595" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
+  <autoFilter ref="A1:F597" xr:uid="{08353A06-E006-45C7-BD45-850F7C3953DF}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F258">
       <sortCondition ref="A1:A188"/>
     </sortState>
